--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,1293 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120226987</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>629149</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6645204</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120228202</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ströbykärret-renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>629156</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6645193</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120226569</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>629132</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6645249</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>8 bladrosettet</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120226893</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>629149</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6645224</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120227130</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ströbykärret-renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>629168</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6645194</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>4 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120226600</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>629132</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6645234</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120227229</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>629156</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6645170</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>10 bladrosettet</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120226812</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>629141</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6645208</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>30 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120227185</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ströbykärret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>629175</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6645179</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120226662</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>629135</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6645228</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>10 bladrosettet</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120226422</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ströbykärrret-Renfanan, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>629117</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6645227</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, en vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2471,10 +2471,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120226987</v>
+        <v>120227185</v>
       </c>
       <c r="B16" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2507,14 +2507,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629149</v>
+        <v>629175</v>
       </c>
       <c r="R16" t="n">
-        <v>6645204</v>
+        <v>6645179</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120228202</v>
+        <v>120226600</v>
       </c>
       <c r="B17" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2624,17 +2624,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629156</v>
+        <v>629132</v>
       </c>
       <c r="R17" t="n">
-        <v>6645193</v>
+        <v>6645234</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2673,7 +2673,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2700,10 +2705,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120226569</v>
+        <v>120226987</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2740,10 +2745,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629132</v>
+        <v>629149</v>
       </c>
       <c r="R18" t="n">
-        <v>6645249</v>
+        <v>6645204</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2775,7 +2780,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2785,12 +2790,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 bladrosettet</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,10 +2822,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226893</v>
+        <v>120226662</v>
       </c>
       <c r="B19" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629149</v>
+        <v>629135</v>
       </c>
       <c r="R19" t="n">
-        <v>6645224</v>
+        <v>6645228</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2892,7 +2897,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2902,12 +2907,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2934,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120227130</v>
+        <v>120226812</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2970,17 +2975,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629168</v>
+        <v>629141</v>
       </c>
       <c r="R20" t="n">
-        <v>6645194</v>
+        <v>6645208</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3009,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3019,12 +3024,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3051,10 +3056,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120226600</v>
+        <v>120226893</v>
       </c>
       <c r="B21" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3091,13 +3096,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629132</v>
+        <v>629149</v>
       </c>
       <c r="R21" t="n">
-        <v>6645234</v>
+        <v>6645224</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3126,7 +3131,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,12 +3141,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3168,10 +3173,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120227229</v>
+        <v>120226569</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3208,10 +3213,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629156</v>
+        <v>629132</v>
       </c>
       <c r="R22" t="n">
-        <v>6645170</v>
+        <v>6645249</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3243,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3253,12 +3258,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,10 +3290,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120226812</v>
+        <v>120228202</v>
       </c>
       <c r="B23" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3321,14 +3326,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629141</v>
+        <v>629156</v>
       </c>
       <c r="R23" t="n">
-        <v>6645208</v>
+        <v>6645193</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3360,7 +3365,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3370,12 +3375,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>30 bladrosetter</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3402,10 +3402,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120227185</v>
+        <v>120227130</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3438,14 +3438,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629175</v>
+        <v>629168</v>
       </c>
       <c r="R24" t="n">
-        <v>6645179</v>
+        <v>6645194</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3487,12 +3487,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,10 +3519,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120226662</v>
+        <v>120226422</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3553,16 +3553,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629135</v>
+        <v>629117</v>
       </c>
       <c r="R25" t="n">
-        <v>6645228</v>
+        <v>6645227</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3594,7 +3598,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3604,12 +3608,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3618,6 +3622,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3636,10 +3641,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120226422</v>
+        <v>120227229</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3670,23 +3675,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629117</v>
+        <v>629156</v>
       </c>
       <c r="R26" t="n">
-        <v>6645227</v>
+        <v>6645170</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3715,7 +3716,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3725,12 +3726,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3739,7 +3740,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -3173,7 +3173,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120226569</v>
+        <v>120228202</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3209,17 +3209,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629132</v>
+        <v>629156</v>
       </c>
       <c r="R22" t="n">
-        <v>6645249</v>
+        <v>6645193</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,12 +3258,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>8 bladrosettet</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,7 +3285,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120228202</v>
+        <v>120226569</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3326,17 +3321,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629156</v>
+        <v>629132</v>
       </c>
       <c r="R23" t="n">
-        <v>6645193</v>
+        <v>6645249</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3365,7 +3360,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3375,7 +3370,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2471,7 +2471,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120227185</v>
+        <v>120226893</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2507,17 +2507,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629175</v>
+        <v>629149</v>
       </c>
       <c r="R16" t="n">
-        <v>6645179</v>
+        <v>6645224</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120226600</v>
+        <v>120226546</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2705,7 +2705,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120226987</v>
+        <v>120228202</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2741,17 +2741,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629149</v>
+        <v>629156</v>
       </c>
       <c r="R18" t="n">
-        <v>6645204</v>
+        <v>6645193</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2790,12 +2790,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>10 bladrosetter</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2822,7 +2817,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226662</v>
+        <v>120226422</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2856,16 +2851,20 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629135</v>
+        <v>629117</v>
       </c>
       <c r="R19" t="n">
-        <v>6645228</v>
+        <v>6645227</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2897,7 +2896,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2907,12 +2906,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2921,6 +2920,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120226812</v>
+        <v>120227185</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2975,17 +2975,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629141</v>
+        <v>629175</v>
       </c>
       <c r="R20" t="n">
-        <v>6645208</v>
+        <v>6645179</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120226893</v>
+        <v>120226662</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629149</v>
+        <v>629135</v>
       </c>
       <c r="R21" t="n">
-        <v>6645224</v>
+        <v>6645228</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,7 +3173,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120228202</v>
+        <v>120226744</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3209,14 +3209,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629156</v>
+        <v>629141</v>
       </c>
       <c r="R22" t="n">
-        <v>6645193</v>
+        <v>6645208</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,7 +3258,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3285,7 +3290,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120226569</v>
+        <v>120226987</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3325,10 +3330,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629132</v>
+        <v>629149</v>
       </c>
       <c r="R23" t="n">
-        <v>6645249</v>
+        <v>6645204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3360,7 +3365,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3370,12 +3375,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>8 bladrosettet</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3402,7 +3407,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120227130</v>
+        <v>120227229</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3438,14 +3443,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629168</v>
+        <v>629156</v>
       </c>
       <c r="R24" t="n">
-        <v>6645194</v>
+        <v>6645170</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3477,7 +3482,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3487,12 +3492,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3519,7 +3524,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120226422</v>
+        <v>120227130</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3553,23 +3558,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629117</v>
+        <v>629168</v>
       </c>
       <c r="R25" t="n">
-        <v>6645227</v>
+        <v>6645194</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3598,7 +3599,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3608,12 +3609,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3622,7 +3623,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3641,7 +3641,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120227229</v>
+        <v>120226569</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629156</v>
+        <v>629132</v>
       </c>
       <c r="R26" t="n">
-        <v>6645170</v>
+        <v>6645249</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2471,7 +2471,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120226893</v>
+        <v>120226662</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629149</v>
+        <v>629135</v>
       </c>
       <c r="R16" t="n">
-        <v>6645224</v>
+        <v>6645228</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120226546</v>
+        <v>120226569</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2631,7 +2631,7 @@
         <v>629132</v>
       </c>
       <c r="R17" t="n">
-        <v>6645234</v>
+        <v>6645249</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2673,12 +2673,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>25 bladrosetter</t>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226422</v>
+        <v>120226812</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2851,20 +2851,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629117</v>
+        <v>629141</v>
       </c>
       <c r="R19" t="n">
-        <v>6645227</v>
+        <v>6645208</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2896,7 +2892,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2906,12 +2902,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2920,7 +2916,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2939,7 +2934,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120227185</v>
+        <v>120226600</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2975,14 +2970,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629175</v>
+        <v>629132</v>
       </c>
       <c r="R20" t="n">
-        <v>6645179</v>
+        <v>6645234</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3014,7 +3009,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,12 +3019,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3056,7 +3051,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120226662</v>
+        <v>120226422</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3090,16 +3085,20 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629135</v>
+        <v>629117</v>
       </c>
       <c r="R21" t="n">
-        <v>6645228</v>
+        <v>6645227</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3131,7 +3130,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3141,12 +3140,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3155,6 +3154,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120226744</v>
+        <v>120227229</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3213,13 +3213,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629141</v>
+        <v>629156</v>
       </c>
       <c r="R22" t="n">
-        <v>6645208</v>
+        <v>6645170</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>25 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,7 +3290,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120226987</v>
+        <v>120226893</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3333,10 +3333,10 @@
         <v>629149</v>
       </c>
       <c r="R23" t="n">
-        <v>6645204</v>
+        <v>6645224</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120227229</v>
+        <v>120227185</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3443,14 +3443,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629156</v>
+        <v>629175</v>
       </c>
       <c r="R24" t="n">
-        <v>6645170</v>
+        <v>6645179</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120227130</v>
+        <v>120226987</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3560,14 +3560,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629168</v>
+        <v>629149</v>
       </c>
       <c r="R25" t="n">
-        <v>6645194</v>
+        <v>6645204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3641,7 +3641,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120226569</v>
+        <v>120227130</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3677,14 +3677,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629132</v>
+        <v>629168</v>
       </c>
       <c r="R26" t="n">
-        <v>6645249</v>
+        <v>6645194</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>8 bladrosettet</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120226569</v>
+        <v>120226422</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2622,19 +2622,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629132</v>
+        <v>629117</v>
       </c>
       <c r="R17" t="n">
-        <v>6645249</v>
+        <v>6645227</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2663,7 +2667,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2673,12 +2677,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>8 bladrosettet</t>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2687,6 +2691,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2705,7 +2710,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120228202</v>
+        <v>120226569</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2741,17 +2746,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629156</v>
+        <v>629132</v>
       </c>
       <c r="R18" t="n">
-        <v>6645193</v>
+        <v>6645249</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2780,7 +2785,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2790,7 +2795,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2817,7 +2827,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226812</v>
+        <v>120226600</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2857,13 +2867,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629141</v>
+        <v>629132</v>
       </c>
       <c r="R19" t="n">
-        <v>6645208</v>
+        <v>6645234</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2892,7 +2902,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2902,12 +2912,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2934,7 +2944,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120226600</v>
+        <v>120226744</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2974,13 +2984,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629132</v>
+        <v>629141</v>
       </c>
       <c r="R20" t="n">
-        <v>6645234</v>
+        <v>6645208</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3009,7 +3019,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3019,12 +3029,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3051,7 +3061,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120226422</v>
+        <v>120228202</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3085,20 +3095,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629117</v>
+        <v>629156</v>
       </c>
       <c r="R21" t="n">
-        <v>6645227</v>
+        <v>6645193</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3130,7 +3136,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3140,12 +3146,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,7 +3155,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120227229</v>
+        <v>120227185</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3209,14 +3209,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629156</v>
+        <v>629175</v>
       </c>
       <c r="R22" t="n">
-        <v>6645170</v>
+        <v>6645179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,7 +3290,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120226893</v>
+        <v>120226987</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3333,10 +3333,10 @@
         <v>629149</v>
       </c>
       <c r="R23" t="n">
-        <v>6645224</v>
+        <v>6645204</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120227185</v>
+        <v>120226893</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3443,17 +3443,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629175</v>
+        <v>629149</v>
       </c>
       <c r="R24" t="n">
-        <v>6645179</v>
+        <v>6645224</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120226987</v>
+        <v>120227130</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3560,14 +3560,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629149</v>
+        <v>629168</v>
       </c>
       <c r="R25" t="n">
-        <v>6645204</v>
+        <v>6645194</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3641,7 +3641,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120227130</v>
+        <v>120227229</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3677,14 +3677,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629168</v>
+        <v>629156</v>
       </c>
       <c r="R26" t="n">
-        <v>6645194</v>
+        <v>6645170</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2471,7 +2471,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120226662</v>
+        <v>120226893</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629135</v>
+        <v>629149</v>
       </c>
       <c r="R16" t="n">
-        <v>6645228</v>
+        <v>6645224</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120226422</v>
+        <v>120226569</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2622,23 +2622,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629117</v>
+        <v>629132</v>
       </c>
       <c r="R17" t="n">
-        <v>6645227</v>
+        <v>6645249</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2667,7 +2663,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2677,12 +2673,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2691,7 +2687,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2710,7 +2705,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120226569</v>
+        <v>120226546</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2753,7 +2748,7 @@
         <v>629132</v>
       </c>
       <c r="R18" t="n">
-        <v>6645249</v>
+        <v>6645234</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2795,12 +2790,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>8 bladrosettet</t>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2827,7 +2822,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226600</v>
+        <v>120226662</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2867,13 +2862,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629132</v>
+        <v>629135</v>
       </c>
       <c r="R19" t="n">
-        <v>6645234</v>
+        <v>6645228</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2902,7 +2897,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2912,12 +2907,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2944,7 +2939,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120226744</v>
+        <v>120228202</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2980,14 +2975,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629141</v>
+        <v>629156</v>
       </c>
       <c r="R20" t="n">
-        <v>6645208</v>
+        <v>6645193</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3019,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3029,12 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3061,7 +3051,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120228202</v>
+        <v>120226422</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3095,16 +3085,20 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629156</v>
+        <v>629117</v>
       </c>
       <c r="R21" t="n">
-        <v>6645193</v>
+        <v>6645227</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3136,7 +3130,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3146,7 +3140,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3155,6 +3154,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120227185</v>
+        <v>120227130</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3209,14 +3209,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629175</v>
+        <v>629168</v>
       </c>
       <c r="R22" t="n">
-        <v>6645179</v>
+        <v>6645194</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,7 +3290,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120226987</v>
+        <v>120226812</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3330,13 +3330,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629149</v>
+        <v>629141</v>
       </c>
       <c r="R23" t="n">
-        <v>6645204</v>
+        <v>6645208</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,7 +3407,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120226893</v>
+        <v>120227229</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3447,13 +3447,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629149</v>
+        <v>629156</v>
       </c>
       <c r="R24" t="n">
-        <v>6645224</v>
+        <v>6645170</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3524,7 +3524,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120227130</v>
+        <v>120226987</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3560,14 +3560,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629168</v>
+        <v>629149</v>
       </c>
       <c r="R25" t="n">
-        <v>6645194</v>
+        <v>6645204</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3641,7 +3641,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120227229</v>
+        <v>120227185</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3677,14 +3677,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629156</v>
+        <v>629175</v>
       </c>
       <c r="R26" t="n">
-        <v>6645170</v>
+        <v>6645179</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2471,7 +2471,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120226893</v>
+        <v>120227185</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2507,17 +2507,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629149</v>
+        <v>629175</v>
       </c>
       <c r="R16" t="n">
-        <v>6645224</v>
+        <v>6645179</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120226569</v>
+        <v>120226422</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2622,19 +2622,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629132</v>
+        <v>629117</v>
       </c>
       <c r="R17" t="n">
-        <v>6645249</v>
+        <v>6645227</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2663,7 +2667,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2673,12 +2677,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>8 bladrosettet</t>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2687,6 +2691,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2705,7 +2710,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120226546</v>
+        <v>120226987</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2745,10 +2750,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629132</v>
+        <v>629149</v>
       </c>
       <c r="R18" t="n">
-        <v>6645234</v>
+        <v>6645204</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2780,7 +2785,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2790,12 +2795,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>25 bladrosetter</t>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2822,7 +2827,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226662</v>
+        <v>120226600</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2862,13 +2867,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629135</v>
+        <v>629132</v>
       </c>
       <c r="R19" t="n">
-        <v>6645228</v>
+        <v>6645234</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2897,7 +2902,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2907,12 +2912,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2939,7 +2944,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120228202</v>
+        <v>120226662</v>
       </c>
       <c r="B20" t="n">
         <v>97930</v>
@@ -2975,14 +2980,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>629156</v>
+        <v>629135</v>
       </c>
       <c r="R20" t="n">
-        <v>6645193</v>
+        <v>6645228</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3014,7 +3019,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3029,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3051,7 +3061,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120226422</v>
+        <v>120227229</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3085,23 +3095,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>629117</v>
+        <v>629156</v>
       </c>
       <c r="R21" t="n">
-        <v>6645227</v>
+        <v>6645170</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3130,7 +3136,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3140,12 +3146,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3154,7 +3160,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3173,7 +3178,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120227130</v>
+        <v>120226893</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3209,17 +3214,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629168</v>
+        <v>629149</v>
       </c>
       <c r="R22" t="n">
-        <v>6645194</v>
+        <v>6645224</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3248,7 +3253,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,12 +3263,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3290,7 +3295,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120226812</v>
+        <v>120227130</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3326,17 +3331,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629141</v>
+        <v>629168</v>
       </c>
       <c r="R23" t="n">
-        <v>6645208</v>
+        <v>6645194</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3365,7 +3370,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3375,12 +3380,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3407,7 +3412,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120227229</v>
+        <v>120226569</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3447,10 +3452,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>629156</v>
+        <v>629132</v>
       </c>
       <c r="R24" t="n">
-        <v>6645170</v>
+        <v>6645249</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3482,7 +3487,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3492,12 +3497,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>10 bladrosettet</t>
+          <t>8 bladrosettet</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3524,7 +3529,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120226987</v>
+        <v>120226812</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3564,13 +3569,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629149</v>
+        <v>629141</v>
       </c>
       <c r="R25" t="n">
-        <v>6645204</v>
+        <v>6645208</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3599,7 +3604,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3609,12 +3614,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>30 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3641,7 +3646,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120227185</v>
+        <v>120228202</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3677,17 +3682,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629175</v>
+        <v>629156</v>
       </c>
       <c r="R26" t="n">
-        <v>6645179</v>
+        <v>6645193</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3716,7 +3721,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3726,12 +3731,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 27389-2021 artfynd.xlsx
+++ b/artfynd/A 27389-2021 artfynd.xlsx
@@ -2471,7 +2471,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120227185</v>
+        <v>120227229</v>
       </c>
       <c r="B16" t="n">
         <v>97930</v>
@@ -2507,14 +2507,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ströbykärret-Renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>629175</v>
+        <v>629156</v>
       </c>
       <c r="R16" t="n">
-        <v>6645179</v>
+        <v>6645170</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosettet</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2588,7 +2588,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120226422</v>
+        <v>120226744</v>
       </c>
       <c r="B17" t="n">
         <v>97930</v>
@@ -2622,20 +2622,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>629117</v>
+        <v>629141</v>
       </c>
       <c r="R17" t="n">
-        <v>6645227</v>
+        <v>6645208</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2667,7 +2663,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2677,12 +2673,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>10 bladrosetter, en vinterståndare.</t>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2691,7 +2687,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2710,7 +2705,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120226987</v>
+        <v>120226600</v>
       </c>
       <c r="B18" t="n">
         <v>97930</v>
@@ -2750,10 +2745,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>629149</v>
+        <v>629132</v>
       </c>
       <c r="R18" t="n">
-        <v>6645204</v>
+        <v>6645234</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2785,7 +2780,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2795,12 +2790,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>10 bladrosetter</t>
+          <t>20 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2827,7 +2822,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120226600</v>
+        <v>120227130</v>
       </c>
       <c r="B19" t="n">
         <v>97930</v>
@@ -2863,14 +2858,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>629132</v>
+        <v>629168</v>
       </c>
       <c r="R19" t="n">
-        <v>6645234</v>
+        <v>6645194</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2902,7 +2897,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2912,12 +2907,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>20 bladrosetter</t>
+          <t>4 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3061,7 +3056,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120227229</v>
+        <v>120228202</v>
       </c>
       <c r="B21" t="n">
         <v>97930</v>
@@ -3097,17 +3092,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-renfanan, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
         <v>629156</v>
       </c>
       <c r="R21" t="n">
-        <v>6645170</v>
+        <v>6645193</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3136,7 +3131,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3146,12 +3141,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:04</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10 bladrosettet</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3178,7 +3168,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120226893</v>
+        <v>120226422</v>
       </c>
       <c r="B22" t="n">
         <v>97930</v>
@@ -3212,16 +3202,20 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>629149</v>
+        <v>629117</v>
       </c>
       <c r="R22" t="n">
-        <v>6645224</v>
+        <v>6645227</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3253,7 +3247,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3263,12 +3257,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>10 bladrosetter, en vinterståndare.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,6 +3271,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3295,7 +3290,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120227130</v>
+        <v>120226893</v>
       </c>
       <c r="B23" t="n">
         <v>97930</v>
@@ -3331,17 +3326,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>629168</v>
+        <v>629149</v>
       </c>
       <c r="R23" t="n">
-        <v>6645194</v>
+        <v>6645224</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3370,7 +3365,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3380,12 +3375,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>4 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3529,7 +3524,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120226812</v>
+        <v>120227185</v>
       </c>
       <c r="B25" t="n">
         <v>97930</v>
@@ -3565,17 +3560,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ströbykärrret-Renfanan, Upl</t>
+          <t>Ströbykärret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>629141</v>
+        <v>629175</v>
       </c>
       <c r="R25" t="n">
-        <v>6645208</v>
+        <v>6645179</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3604,7 +3599,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3614,12 +3609,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>30 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3646,7 +3641,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120228202</v>
+        <v>120226987</v>
       </c>
       <c r="B26" t="n">
         <v>97930</v>
@@ -3682,17 +3677,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ströbykärret-renfanan, Upl</t>
+          <t>Ströbykärrret-Renfanan, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>629156</v>
+        <v>629149</v>
       </c>
       <c r="R26" t="n">
-        <v>6645193</v>
+        <v>6645204</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3721,7 +3716,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3731,7 +3726,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>10 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
